--- a/downloads/suppliers.xlsx
+++ b/downloads/suppliers.xlsx
@@ -436,10 +436,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>27 טסט</v>
+        <v>21שרה טס</v>
       </c>
       <c r="B2" t="str">
-        <v>190420264</v>
+        <v>1904202677</v>
       </c>
       <c r="C2" t="str">
         <v>10</v>
